--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
   <si>
     <t>Filename</t>
   </si>
@@ -808,691 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9824,0.0007,0.0087,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0096,0.0000,0.0000,0.9988</t>
+    <t>0.9985,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0002,0.0000,0.0028</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.0000,0.9998</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9788,0.0193,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.4725,0.0008,0.6123,0.0003</t>
+  </si>
+  <si>
+    <t>0.0624,0.0008,0.9582,0.0000</t>
+  </si>
+  <si>
+    <t>0.9259,0.0008,0.0882,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.0704,0.9413,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9902,0.0001,0.0069,0.0001</t>
+  </si>
+  <si>
+    <t>0.9509,0.0014,0.0425,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0251,0.0009,0.9686,0.0010</t>
+  </si>
+  <si>
+    <t>0.0508,0.0001,0.9726,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9989,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.1455,0.8705,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9925,0.0035,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9990,0.0014</t>
+  </si>
+  <si>
+    <t>0.0187,0.6782,0.1276,0.0000</t>
+  </si>
+  <si>
+    <t>0.9846,0.0083,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.1385,0.0016,0.8763,0.0025</t>
+  </si>
+  <si>
+    <t>0.0053,0.9938,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0062,0.9895,0.0038,0.0007</t>
+  </si>
+  <si>
+    <t>0.0268,0.4583,0.2921,0.0065</t>
+  </si>
+  <si>
+    <t>0.0023,0.0016,0.9917,0.0014</t>
+  </si>
+  <si>
+    <t>0.0080,0.0002,0.9898,0.0003</t>
+  </si>
+  <si>
+    <t>0.0428,0.0001,0.9391,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0089,0.9978,0.0005</t>
+  </si>
+  <si>
+    <t>0.0119,0.9742,0.0059,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9821,0.0006,0.7673</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0171,0.9942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.0004,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0028,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0063,0.9995,0.0012</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0020,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.5762,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.0002,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9922,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9994,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8006,0.0028,0.2388,0.0000</t>
+  </si>
+  <si>
+    <t>0.9300,0.0642,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9756,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9941,0.9317,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0382,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9882,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0155,0.9990</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9146,0.9121,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0170,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9028,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9948,0.3143,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9844,0.0254,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0012,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9968,0.0042,0.0002,0.0000</t>
+  </si>
+  <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9902,0.0139,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0019,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0001,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0671,0.0001,0.9483,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9987,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8751,0.1631,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.1374,0.0067,0.8374,0.0006</t>
+  </si>
+  <si>
+    <t>0.8412,0.0006,0.2132,0.0001</t>
+  </si>
+  <si>
+    <t>0.9612,0.0051,0.0062,0.0023</t>
+  </si>
+  <si>
+    <t>0.9491,0.0040,0.0257,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0248,0.0003,0.9973</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0399,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9216,0.0790,0.0053,0.0002</t>
+  </si>
+  <si>
+    <t>0.5361,0.4215,0.0062,0.0006</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9931,0.0020,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.6946,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9817,0.9971,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.7226,0.0445,0.1112,0.0026</t>
+  </si>
+  <si>
+    <t>0.0302,0.0003,0.9751,0.0002</t>
+  </si>
+  <si>
+    <t>0.9544,0.0014,0.0265,0.0012</t>
+  </si>
+  <si>
+    <t>0.0250,0.0001,0.0000,0.9940</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9659,0.9816,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0392,0.9664,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.3784,0.6824,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.4087,0.0000,0.0007,0.7306</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.2590,0.0102,0.7547,0.0031</t>
+  </si>
+  <si>
+    <t>0.9895,0.0001,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.9849,0.0018,0.0025,0.0045</t>
+  </si>
+  <si>
+    <t>0.1750,0.8224,0.0032,0.0009</t>
+  </si>
+  <si>
+    <t>0.9959,0.0011,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0031,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.3365,0.6213,0.0049,0.0007</t>
+  </si>
+  <si>
+    <t>0.8287,0.1150,0.0140,0.0008</t>
+  </si>
+  <si>
+    <t>0.9962,0.0009,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0021,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.2078,0.7878,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.8561,0.1421,0.0056,0.0001</t>
+  </si>
+  <si>
+    <t>0.9327,0.0754,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.8224,0.0728,0.0819,0.0014</t>
+  </si>
+  <si>
+    <t>0.9956,0.0064,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8935,0.1403,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9766,0.0115,0.0081,0.0018</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0009,0.9982,0.0015</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0001,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0009,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0047,0.9906,0.0004</t>
+  </si>
+  <si>
+    <t>0.0061,0.0007,0.9916,0.0002</t>
+  </si>
+  <si>
+    <t>0.0104,0.3029,0.5999,0.0008</t>
+  </si>
+  <si>
+    <t>0.0052,0.0030,0.9874,0.0004</t>
+  </si>
+  <si>
+    <t>0.0071,0.0401,0.9645,0.0004</t>
+  </si>
+  <si>
+    <t>0.7616,0.0020,0.2420,0.0003</t>
+  </si>
+  <si>
+    <t>0.1809,0.0032,0.7904,0.0029</t>
+  </si>
+  <si>
+    <t>0.2862,0.0209,0.5056,0.0005</t>
+  </si>
+  <si>
+    <t>0.8567,0.2412,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9980,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0820,0.9282,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9131,0.1085,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9988,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8995,0.0313,0.0193,0.0008</t>
+  </si>
+  <si>
+    <t>0.9419,0.0005,0.0591,0.0004</t>
+  </si>
+  <si>
+    <t>0.9961,0.0002,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9405,0.0010,0.0525,0.0005</t>
+  </si>
+  <si>
+    <t>0.6064,0.0006,0.3920,0.0020</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0019</t>
+  </si>
+  <si>
+    <t>0.0030,0.0107,0.9893,0.0023</t>
+  </si>
+  <si>
+    <t>0.0019,0.7746,0.8763,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.1359,0.9605,0.0011</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9938,0.0035,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0118,0.9972,0.0063</t>
+  </si>
+  <si>
+    <t>0.0254,0.3039,0.5275,0.0044</t>
+  </si>
+  <si>
+    <t>0.9958,0.0000,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0119,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0146,0.0019,0.9831,0.0004</t>
+  </si>
+  <si>
+    <t>0.0112,0.0000,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0454,0.0021,0.9318,0.0024</t>
+  </si>
+  <si>
+    <t>0.0006,0.0310,0.9961,0.0008</t>
+  </si>
+  <si>
+    <t>0.9943,0.0000,0.0065,0.0000</t>
+  </si>
+  <si>
+    <t>0.9835,0.0001,0.0166,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0000,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
     <t>0.9991,0.0005,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0050,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.1318,0.0019,0.8987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0021,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.9655,0.0002,0.0440,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0003,0.9945,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.0425,0.9602,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9813,0.0003,0.0154,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0003,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0030,0.0004,0.9930,0.0026</t>
-  </si>
-  <si>
-    <t>0.0168,0.0006,0.9849,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9995,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.2442,0.7757,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9711,0.0167,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9989,0.0040</t>
-  </si>
-  <si>
-    <t>0.0042,0.8663,0.1449,0.0000</t>
-  </si>
-  <si>
-    <t>0.9947,0.0019,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0866,0.0020,0.9096,0.0036</t>
-  </si>
-  <si>
-    <t>0.0054,0.9930,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.0025,0.9898,0.0089,0.0032</t>
-  </si>
-  <si>
-    <t>0.0044,0.8243,0.2378,0.0021</t>
-  </si>
-  <si>
-    <t>0.0059,0.0017,0.9868,0.0022</t>
-  </si>
-  <si>
-    <t>0.0429,0.0006,0.9570,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.0001,0.9944,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0011,0.9971,0.0003</t>
-  </si>
-  <si>
-    <t>0.0032,0.9951,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9435,0.0003,0.9329</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.1913,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9977,0.0012</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0003,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.9926,0.0060,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9957,0.0012,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0006,0.9992,0.0005</t>
-  </si>
-  <si>
-    <t>0.9937,0.0011,0.0011,0.0020</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0011,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.5186,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0031,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9903,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9978,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9862,0.0051,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.9141,0.0865,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0038,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9936,0.9091,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.3922,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9728,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0008,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.1915,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9956,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9821,0.9784,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.5955,0.9942,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9526,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.8522,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9936,0.0075,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0290,0.9954,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9996,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9992,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.9963,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2382,0.7880,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.2505,0.0049,0.6714,0.0035</t>
-  </si>
-  <si>
-    <t>0.9103,0.0008,0.0879,0.0006</t>
-  </si>
-  <si>
-    <t>0.6898,0.0664,0.0586,0.0014</t>
-  </si>
-  <si>
-    <t>0.6279,0.0014,0.3542,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.6901,0.0008,0.9662</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.6640,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.7597,0.2405,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.0832,0.8920,0.0071,0.0010</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0007,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.4380,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.2237,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4490,0.0411,0.3631,0.0027</t>
-  </si>
-  <si>
-    <t>0.9253,0.0002,0.1035,0.0000</t>
-  </si>
-  <si>
-    <t>0.9301,0.0009,0.0605,0.0008</t>
-  </si>
-  <si>
-    <t>0.3566,0.0000,0.0000,0.8912</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9942,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0264,0.9721,0.0012,0.0022</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.4844,0.5514,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9969,0.0004,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.5877,0.0000,0.0007,0.5573</t>
-  </si>
-  <si>
-    <t>0.9928,0.0005,0.0031,0.0017</t>
-  </si>
-  <si>
-    <t>0.0588,0.0468,0.9174,0.0083</t>
-  </si>
-  <si>
-    <t>0.9866,0.0001,0.0025,0.0034</t>
-  </si>
-  <si>
-    <t>0.9928,0.0008,0.0011,0.0023</t>
-  </si>
-  <si>
-    <t>0.7618,0.2314,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0004,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9696,0.0270,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.2865,0.6811,0.0042,0.0005</t>
-  </si>
-  <si>
-    <t>0.9283,0.0303,0.0173,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9975,0.0008,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0014,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.0432,0.9545,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.2920,0.6561,0.0106,0.0002</t>
-  </si>
-  <si>
-    <t>0.8902,0.0937,0.0073,0.0002</t>
-  </si>
-  <si>
-    <t>0.0142,0.1965,0.9647,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9782,0.0260,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0009,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.9911,0.0034,0.0022,0.0012</t>
-  </si>
-  <si>
-    <t>0.0010,0.0019,0.9975,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0040,0.9881,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0083,0.0077,0.9691,0.0016</t>
-  </si>
-  <si>
-    <t>0.0246,0.0876,0.8395,0.0003</t>
-  </si>
-  <si>
-    <t>0.0358,0.0187,0.9028,0.0013</t>
-  </si>
-  <si>
-    <t>0.8969,0.0027,0.0880,0.0003</t>
-  </si>
-  <si>
-    <t>0.5582,0.0440,0.0635,0.0187</t>
-  </si>
-  <si>
-    <t>0.8417,0.0128,0.0922,0.0008</t>
-  </si>
-  <si>
-    <t>0.0084,0.9921,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9988,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.1740,0.8619,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.4362,0.6700,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.9962,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0016,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9691,0.0003,0.0326,0.0001</t>
-  </si>
-  <si>
-    <t>0.9773,0.0034,0.0053,0.0035</t>
-  </si>
-  <si>
-    <t>0.9838,0.0004,0.0074,0.0005</t>
-  </si>
-  <si>
-    <t>0.6975,0.0039,0.2836,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9991,0.0011</t>
-  </si>
-  <si>
-    <t>0.0013,0.0011,0.9935,0.0028</t>
-  </si>
-  <si>
-    <t>0.0010,0.8030,0.9115,0.0002</t>
-  </si>
-  <si>
-    <t>0.0805,0.0009,0.9156,0.0005</t>
-  </si>
-  <si>
-    <t>0.0024,0.0918,0.9754,0.0002</t>
-  </si>
-  <si>
-    <t>0.9957,0.0039,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0010,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0037,0.9990,0.0022</t>
-  </si>
-  <si>
-    <t>0.0108,0.9337,0.0405,0.0036</t>
-  </si>
-  <si>
-    <t>0.9859,0.0003,0.0072,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.0231,0.9811,0.0005</t>
-  </si>
-  <si>
-    <t>0.0029,0.0012,0.9945,0.0003</t>
-  </si>
-  <si>
-    <t>0.0065,0.0001,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0014,0.9955,0.0010</t>
-  </si>
-  <si>
-    <t>0.0006,0.1484,0.9928,0.0005</t>
-  </si>
-  <si>
-    <t>0.9972,0.0000,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.9621,0.0002,0.0433,0.0001</t>
-  </si>
-  <si>
-    <t>0.9681,0.0002,0.0316,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0021,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0219,0.0013,0.9744,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0025,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.0152,0.0023,0.9691,0.0019</t>
-  </si>
-  <si>
-    <t>0.0040,0.0019,0.9896,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.8568,0.0006,0.0557,0.0081</t>
-  </si>
-  <si>
-    <t>0.0127,0.0026,0.9756,0.0040</t>
-  </si>
-  <si>
-    <t>0.0054,0.0000,0.9881,0.0013</t>
-  </si>
-  <si>
-    <t>0.9921,0.0000,0.0001,0.0085</t>
-  </si>
-  <si>
-    <t>0.0001,0.0152,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0144,0.0000,0.0004,0.9961</t>
-  </si>
-  <si>
-    <t>0.8796,0.0127,0.0026,0.0485</t>
+    <t>0.9912,0.0074,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0006,0.9916,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0047,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0357,0.0072,0.9377,0.0015</t>
+  </si>
+  <si>
+    <t>0.0084,0.0126,0.9407,0.0018</t>
+  </si>
+  <si>
+    <t>0.0588,0.0013,0.9188,0.0068</t>
+  </si>
+  <si>
+    <t>0.0025,0.0028,0.9925,0.0010</t>
+  </si>
+  <si>
+    <t>0.2956,0.0001,0.5913,0.0016</t>
+  </si>
+  <si>
+    <t>0.9912,0.0000,0.0018,0.0023</t>
+  </si>
+  <si>
+    <t>0.0004,0.0064,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.0116,0.0001,0.0011,0.9957</t>
+  </si>
+  <si>
+    <t>0.9525,0.0012,0.0008,0.0307</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1892,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1906,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1920,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1934,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1948,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1962,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1976,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1990,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2004,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2018,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2393,7 +2390,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2491,7 +2488,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2522,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2536,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2816,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2942,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>267</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>267</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,7 +3009,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3040,7 +3037,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3051,10 +3048,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,10 +3076,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3110,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3124,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3138,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>273</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3180,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3194,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3222,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>270</v>
+        <v>354</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3236,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>354</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3250,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>354</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3264,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3306,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3446,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>365</v>
+        <v>285</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3457,7 +3454,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>366</v>
@@ -3527,7 +3524,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>371</v>
@@ -3544,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3572,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,10 +3580,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3614,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,10 +3622,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3712,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3726,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3740,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3751,10 +3748,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3765,10 +3762,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3782,7 +3779,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3796,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3810,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>270</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3824,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,10 +3832,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3852,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3866,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3880,7 +3877,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>267</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3922,7 +3919,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3947,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3978,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4006,7 +4003,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4031,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,10 +4070,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4104,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4118,7 +4115,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4146,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4160,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4258,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>357</v>
+        <v>416</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4272,7 +4269,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,10 +4280,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4300,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,10 +4308,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4328,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4342,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4356,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4370,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4384,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4398,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4412,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>328</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4468,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>328</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4496,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4510,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4524,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4538,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4552,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4566,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4580,7 +4577,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4605,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4636,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4650,7 +4647,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,10 +4658,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4678,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4692,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4706,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4720,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4734,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4748,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4762,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4776,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4790,7 +4787,7 @@
         <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4804,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4818,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4832,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4846,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>381</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4930,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>462</v>
+        <v>275</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,7 +5011,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5140,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>476</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5210,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5224,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5238,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5308,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>485</v>
+        <v>427</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,10 +5316,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5364,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>338</v>
+        <v>267</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5417,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>267</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5434,7 +5431,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
